--- a/testdata/mobile/Login.xlsx
+++ b/testdata/mobile/Login.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Sales Force\Automation\stp-automation-test\testdata\mobile\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Sales Force\Automation\sales-force-automation-test\testdata\mobile\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19B03084-0365-47E8-AA62-7D775768C061}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3059647C-3BC9-4B67-B809-69C9F327A209}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sales" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="5">
   <si>
     <t>email</t>
   </si>
@@ -45,13 +45,10 @@
     <t>expectedCondition</t>
   </si>
   <si>
-    <t>Password123</t>
-  </si>
-  <si>
     <t>Welcome back</t>
   </si>
   <si>
-    <t>Santi.nurmala@yopmail.com</t>
+    <t>fajarsetiawan@yopmail.com</t>
   </si>
 </sst>
 </file>
@@ -387,15 +384,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="29.21875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="42.88671875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="29.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="42.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -406,15 +403,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
         <v>3</v>
-      </c>
-      <c r="C2" t="s">
-        <v>4</v>
       </c>
     </row>
   </sheetData>
